--- a/jobs/_bundles/dip_r4a_signal_monitor/assets/assets.xlsx
+++ b/jobs/_bundles/dip_r4a_signal_monitor/assets/assets.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,1200 +419,1200 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>苹果公司</t>
+          <t>华神科技</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>AAPL.O</t>
+          <t>SZ000790</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>微软</t>
+          <t>新城控股</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MSFT.O</t>
+          <t>SH601155</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>英伟达</t>
+          <t>金太阳</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVDA.O</t>
+          <t>SZ300606</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>亚马逊</t>
+          <t>安诺其</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AMZN.O</t>
+          <t>SZ300067</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>元平台</t>
+          <t>芳源股份</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>META.O</t>
+          <t>SH688148</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>谷歌</t>
+          <t>经纬辉开</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GOOGL.O</t>
+          <t>SZ300120</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>迅游科技</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TSLA.O</t>
+          <t>SZ300467</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>博通</t>
+          <t>金时科技</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AVGO.O</t>
+          <t>SZ002951</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>甲骨文</t>
+          <t>ST八菱</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORCL.N</t>
+          <t>SZ002592</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>奈飞</t>
+          <t>ST泉为</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NFLX.O</t>
+          <t>SZ300716</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>超威半导体</t>
+          <t>北新建材</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMD.O</t>
+          <t>SZ000786</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>高通</t>
+          <t>新媒股份</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>QCOM.O</t>
+          <t>SZ300770</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>德州仪器</t>
+          <t>山西汾酒</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TXN.O</t>
+          <t>SH600809</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>思科</t>
+          <t>保立佳</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CSCO.O</t>
+          <t>SZ301037</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>国际商业机器</t>
+          <t>万通智控</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IBM.N</t>
+          <t>SZ300643</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>赛富时</t>
+          <t>江阴银行</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CRM.N</t>
+          <t>SZ002807</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ServiceNow_Inc</t>
+          <t>三维化学</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NOW.N</t>
+          <t>SZ002469</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>财捷</t>
+          <t>中煤能源</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>INTU.O</t>
+          <t>SH601898</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>奥多比</t>
+          <t>恒生电子</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADBE.O</t>
+          <t>SH600570</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应用材料</t>
+          <t>泉峰汽车</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AMAT.O</t>
+          <t>SH603982</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>泛林</t>
+          <t>万泽股份</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LRCX.O</t>
+          <t>SZ000534</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>科磊</t>
+          <t>迈威生物</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KLAC.O</t>
+          <t>SH688062</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>派拓网络</t>
+          <t>蔚蓝锂芯</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PANW.O</t>
+          <t>SZ002245</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CrowdStrike_Holdings_Inc</t>
+          <t>中恒集团</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CRWD.O</t>
+          <t>SH600252</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Palantir_Technologies_Inc</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PLTR.O</t>
+          <t>SZ300502</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Snowflake_Inc</t>
+          <t>奥锐特</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SNOW.N</t>
+          <t>SH605116</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>好市多</t>
+          <t>西点药业</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COST.O</t>
+          <t>SZ301130</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>沃尔玛</t>
+          <t>西藏药业</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WMT.O</t>
+          <t>SH600211</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>家得宝</t>
+          <t>麦格米特</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HD.N</t>
+          <t>SZ002851</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>劳氏</t>
+          <t>航天软件</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LOW.N</t>
+          <t>SH688562</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>麦当劳</t>
+          <t>太平鸟</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MCD.N</t>
+          <t>SH603877</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>耐克</t>
+          <t>新亚电缆</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NKE.N</t>
+          <t>SZ001382</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>星巴克</t>
+          <t>农产品</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SBUX.O</t>
+          <t>SZ000061</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>缤客控股</t>
+          <t>麦加芯彩</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BKNG.O</t>
+          <t>SH603062</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>迪士尼</t>
+          <t>赛腾股份</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DIS.N</t>
+          <t>SH603283</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The_TJX_Companies_Inc</t>
+          <t>三角防务</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TJX.N</t>
+          <t>SZ300775</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>宝洁</t>
+          <t>汇绿生态</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PG.N</t>
+          <t>SZ001267</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>可口可乐</t>
+          <t>嘉泽新能</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KO.N</t>
+          <t>SH601619</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>百事可乐</t>
+          <t>康华生物</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PEP.O</t>
+          <t>SZ300841</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>菲利普莫里斯</t>
+          <t>南新制药</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PM.N</t>
+          <t>SH688189</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>奥驰亚</t>
+          <t>百济神州</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MO.N</t>
+          <t>SH688235</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>T-Mobile_US_Inc</t>
+          <t>中科电气</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TMUS.O</t>
+          <t>SZ300035</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>威瑞森</t>
+          <t>飞凯材料</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VZ.N</t>
+          <t>SZ300398</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>美国电话电报</t>
+          <t>熙菱信息</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>T.N</t>
+          <t>SZ300588</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>康卡斯特</t>
+          <t>大连友谊</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CMCSA.O</t>
+          <t>SZ000679</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>摩根大通</t>
+          <t>东利机械</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPM.N</t>
+          <t>SZ301298</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>美国银行</t>
+          <t>京北方</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BAC.N</t>
+          <t>SZ002987</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>富国银行</t>
+          <t>东百集团</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WFC.N</t>
+          <t>SH600693</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>高盛</t>
+          <t>公牛集团</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GS.N</t>
+          <t>SH603195</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>摩根士丹利</t>
+          <t>金雷股份</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MS.N</t>
+          <t>SZ300443</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>花旗集团</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>C.N</t>
+          <t>SZ002050</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>贝莱德</t>
+          <t>海南高速</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BLK.N</t>
+          <t>SZ000886</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>黑石集团</t>
+          <t>三维股份</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BX.N</t>
+          <t>SH603033</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>嘉信理财</t>
+          <t>珠城科技</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SCHW.N</t>
+          <t>SZ301280</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>第一资本</t>
+          <t>诺力股份</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COF.N</t>
+          <t>SH603611</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>美国运通</t>
+          <t>燕东微</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AXP.N</t>
+          <t>SH688172</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>维萨</t>
+          <t>ST合纵</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>V.N</t>
+          <t>SZ300477</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>万事达</t>
+          <t>中孚信息</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MA.N</t>
+          <t>SZ300659</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>标普全球</t>
+          <t>宝鼎科技</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SPGI.N</t>
+          <t>SZ002552</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>穆迪</t>
+          <t>中邮科技</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MCO.N</t>
+          <t>SH688648</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>芝加哥商品交易所</t>
+          <t>王子新材</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CME.O</t>
+          <t>SZ002735</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>洲际交易所</t>
+          <t>金天钛业</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ICE.N</t>
+          <t>SH688750</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>前进保险</t>
+          <t>阳光诺和</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PGR.N</t>
+          <t>SH688621</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>美国家庭人寿保险</t>
+          <t>惠泰医疗</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AFL.N</t>
+          <t>SH688617</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>礼来</t>
+          <t>新恒汇</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LLY.N</t>
+          <t>SZ301678</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>强生</t>
+          <t>赛升药业</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JNJ.N</t>
+          <t>SZ300485</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>艾伯维</t>
+          <t>誉帆科技</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ABBV.N</t>
+          <t>SZ001396</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>默克</t>
+          <t>卫光生物</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MRK.N</t>
+          <t>SZ002880</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>雅培</t>
+          <t>金龙机电</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ABT.N</t>
+          <t>SZ300032</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>安进</t>
+          <t>博瑞传播</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AMGN.O</t>
+          <t>SH600880</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>联合健康</t>
+          <t>ST晨鸣</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UNH.N</t>
+          <t>SZ000488</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>赛默飞世尔</t>
+          <t>南宁百货</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TMO.N</t>
+          <t>SH600712</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>直觉外科</t>
+          <t>泰坦股份</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ISRG.O</t>
+          <t>SZ003036</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>丹纳赫</t>
+          <t>长青科技</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DHR.N</t>
+          <t>SZ001324</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>美敦力</t>
+          <t>永新股份</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MDT.N</t>
+          <t>SZ002014</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>吉利德科学</t>
+          <t>海利得</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GILD.O</t>
+          <t>SZ002206</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>百时美施贵宝</t>
+          <t>路维光电</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BMY.N</t>
+          <t>SH688401</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>辉瑞</t>
+          <t>浦东金桥</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PFE.N</t>
+          <t>SH600639</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>再生元</t>
+          <t>华菱钢铁</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>REGN.O</t>
+          <t>SZ000932</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>卡特彼勒</t>
+          <t>联建光电</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CAT.N</t>
+          <t>SZ300269</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>迪尔</t>
+          <t>南网科技</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>DE.N</t>
+          <t>SH688248</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>通用电气航空</t>
+          <t>小熊电器</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GE.N</t>
+          <t>SZ002959</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>雷神技术</t>
+          <t>广博股份</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RTX.N</t>
+          <t>SZ002103</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>霍尼韦尔</t>
+          <t>正强股份</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HON.O</t>
+          <t>SZ301119</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>伊顿</t>
+          <t>秦安股份</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ETN.N</t>
+          <t>SH603758</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>洛克希德马丁</t>
+          <t>润贝航科</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LMT.N</t>
+          <t>SZ001316</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>联合包裹</t>
+          <t>中航重机</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UPS.N</t>
+          <t>SH600765</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>联邦快递</t>
+          <t>海特生物</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FDX.N</t>
+          <t>SZ300683</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>废物管理</t>
+          <t>润都股份</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WM.N</t>
+          <t>SZ002923</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>联合租赁</t>
+          <t>易普力</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>URI.N</t>
+          <t>SZ002096</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>埃克森美孚</t>
+          <t>华峰超纤</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>XOM.N</t>
+          <t>SZ300180</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>雪佛龙</t>
+          <t>晶华新材</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVX.N</t>
+          <t>SH603683</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>康菲石油</t>
+          <t>格林达</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>COP.N</t>
+          <t>SH603931</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>斯伦贝谢</t>
+          <t>深圳华强</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SLB.N</t>
+          <t>SZ000062</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>自由港麦克莫兰</t>
+          <t>雄帝科技</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FCX.N</t>
+          <t>SZ300546</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>林德</t>
+          <t>万德斯</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LIN.O</t>
+          <t>SH688178</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>空气化工产品</t>
+          <t>华盛锂电</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>APD.N</t>
+          <t>SH688353</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>新纪元能源</t>
+          <t>怡球资源</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NEE.N</t>
+          <t>SH601388</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>杜克能源</t>
+          <t>太极股份</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DUK.N</t>
+          <t>SZ002368</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>荣昌生物</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SO.N</t>
+          <t>SH688331</t>
         </is>
       </c>
     </row>
